--- a/camp-items.xlsx
+++ b/camp-items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maioc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08ECAC59-73A7-4085-8019-1A11760E9AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56E2A73-9E8C-4F45-91BA-F4B1AC321CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="70">
   <si>
     <t>帳篷限制模式</t>
   </si>
@@ -52,215 +52,184 @@
     <t>大天幕</t>
   </si>
   <si>
+    <t>CC3 專用</t>
+  </si>
+  <si>
+    <t>CC3 達人外帳本體</t>
+  </si>
+  <si>
+    <t>CC3 專用延伸天幕</t>
+  </si>
+  <si>
+    <t>CC3 專用營柱袋</t>
+  </si>
+  <si>
+    <t>CC3 客廳內地墊</t>
+  </si>
+  <si>
+    <t>CC3 內帳專用防潮墊</t>
+  </si>
+  <si>
+    <t>CC3 專用外防潮地布</t>
+  </si>
+  <si>
+    <t>63充氣帳專用</t>
+  </si>
+  <si>
+    <t>延伸天幕</t>
+  </si>
+  <si>
+    <t>內帳專用防潮墊</t>
+  </si>
+  <si>
+    <t>外防潮地布</t>
+  </si>
+  <si>
+    <t>高功率打氣機</t>
+  </si>
+  <si>
     <t>通用</t>
   </si>
   <si>
-    <t>天幕營柱</t>
-  </si>
-  <si>
-    <t>營釘&amp;營鎚</t>
-  </si>
-  <si>
-    <t>營繩</t>
-  </si>
-  <si>
-    <t>豬尾巴</t>
-  </si>
-  <si>
     <t>睡眠與寢具</t>
   </si>
   <si>
+    <t>內地墊</t>
+  </si>
+  <si>
+    <t>營丁營繩包</t>
+  </si>
+  <si>
+    <t>營柱</t>
+  </si>
+  <si>
     <t>睡袋</t>
   </si>
   <si>
     <t>枕頭</t>
   </si>
   <si>
-    <t>床墊</t>
+    <t>睡墊</t>
   </si>
   <si>
     <t>床包</t>
   </si>
   <si>
-    <t>內地墊</t>
-  </si>
-  <si>
     <t>電力與照明</t>
   </si>
   <si>
-    <t>戶外動力延長線</t>
-  </si>
-  <si>
-    <t>燈</t>
-  </si>
-  <si>
-    <t>夜衝路燈</t>
-  </si>
-  <si>
-    <t>鼓風機</t>
-  </si>
-  <si>
-    <t>鼓風機長管</t>
+    <t>電線</t>
+  </si>
+  <si>
+    <t>燈具(包含夜衝燈)</t>
+  </si>
+  <si>
+    <t>鼓風機(包含長管)</t>
+  </si>
+  <si>
+    <t>桌子</t>
+  </si>
+  <si>
+    <t>椅子</t>
   </si>
   <si>
     <t>廚房野炊</t>
   </si>
   <si>
-    <t>保冰桶 / 冰磚</t>
+    <t>餐具</t>
+  </si>
+  <si>
+    <t>曬網籃與豬尾巴</t>
+  </si>
+  <si>
+    <t>垃圾架</t>
+  </si>
+  <si>
+    <t>衛生與個人</t>
+  </si>
+  <si>
+    <t>濕紙巾衛生紙</t>
+  </si>
+  <si>
+    <t>換洗衣物</t>
+  </si>
+  <si>
+    <t>浴巾</t>
+  </si>
+  <si>
+    <t>洗漱用品</t>
+  </si>
+  <si>
+    <t>醫療與防護</t>
+  </si>
+  <si>
+    <t>防蚊,急救小包,蚊子藥,防曬</t>
+  </si>
+  <si>
+    <t>蚊帳</t>
+  </si>
+  <si>
+    <t>雜物箱</t>
+  </si>
+  <si>
+    <t>RV桶</t>
+  </si>
+  <si>
+    <t>冬季/寒流加帶</t>
+  </si>
+  <si>
+    <t>季節客製化</t>
+  </si>
+  <si>
+    <t>暖爐(一氧化碳偵測器)or發熱毯</t>
   </si>
   <si>
     <t>非必要</t>
   </si>
   <si>
-    <t>卡式瓦斯爐</t>
-  </si>
-  <si>
-    <t>卡式瓦斯罐</t>
+    <t>冰箱or保冰的</t>
+  </si>
+  <si>
+    <t>瓦斯爐(包含瓦斯)</t>
+  </si>
+  <si>
+    <t>鍋具</t>
+  </si>
+  <si>
+    <t>行軍床</t>
+  </si>
+  <si>
+    <t>電扇</t>
   </si>
   <si>
     <t>擋風板</t>
   </si>
   <si>
-    <t>多功能套鍋組</t>
+    <t>蛋捲桌</t>
   </si>
   <si>
     <t>廚具收納袋</t>
   </si>
   <si>
-    <t>個人碗盤餐具</t>
-  </si>
-  <si>
-    <t>吊掛瀝水網</t>
-  </si>
-  <si>
     <t>洗碗精</t>
   </si>
   <si>
     <t>垃圾袋</t>
   </si>
   <si>
-    <t>行軍床</t>
-  </si>
-  <si>
-    <t>衛生與個人</t>
-  </si>
-  <si>
-    <t>大浴巾</t>
-  </si>
-  <si>
-    <t>換洗衣物</t>
-  </si>
-  <si>
-    <t>洗漱用品</t>
-  </si>
-  <si>
-    <t>垃圾架</t>
-  </si>
-  <si>
-    <t>醫療與防護</t>
-  </si>
-  <si>
     <t>個人常備藥</t>
   </si>
   <si>
-    <t>強效防蚊液</t>
-  </si>
-  <si>
-    <t>防曬乳</t>
-  </si>
-  <si>
-    <t>急救小包</t>
-  </si>
-  <si>
-    <t>止癢藥膏</t>
-  </si>
-  <si>
-    <t>排流扇</t>
-  </si>
-  <si>
-    <t>防蚊網帳</t>
-  </si>
-  <si>
     <t>蚊香</t>
   </si>
   <si>
-    <t>桌子</t>
-  </si>
-  <si>
-    <t>椅子</t>
-  </si>
-  <si>
-    <t>雜物箱</t>
-  </si>
-  <si>
-    <t>RV 桶</t>
-  </si>
-  <si>
-    <t>冬季/寒流加帶</t>
-  </si>
-  <si>
-    <t>季節客製化</t>
-  </si>
-  <si>
-    <t>煤油暖爐</t>
-  </si>
-  <si>
-    <t>一氧化碳警報器</t>
-  </si>
-  <si>
-    <t>雙人電熱毯</t>
-  </si>
-  <si>
     <t>夏季加帶</t>
   </si>
   <si>
     <t>製冰機</t>
   </si>
   <si>
-    <t>CC3 專用</t>
-  </si>
-  <si>
-    <t>CC3 達人外帳本體</t>
-  </si>
-  <si>
-    <t>CC3 專用延伸天幕</t>
-  </si>
-  <si>
-    <t>CC3 專用營柱袋</t>
-  </si>
-  <si>
-    <t>CC3 客廳內地墊</t>
-  </si>
-  <si>
-    <t>CC3 內帳專用防潮墊</t>
-  </si>
-  <si>
-    <t>CC3 專用外防潮地布</t>
-  </si>
-  <si>
-    <t>63充氣帳專用</t>
-  </si>
-  <si>
-    <t>外帳本體</t>
-  </si>
-  <si>
-    <t>延伸天幕</t>
-  </si>
-  <si>
-    <t>內帳專用防潮墊</t>
-  </si>
-  <si>
-    <t>外防潮地布</t>
-  </si>
-  <si>
-    <t>高功率打氣機</t>
-  </si>
-  <si>
-    <t>蛋捲桌</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>濕紙巾 / 衛生紙</t>
+    <t>帳篷本體</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -695,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="5" bestFit="1" customWidth="1"/>
@@ -821,10 +790,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>7</v>
@@ -835,10 +804,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>7</v>
@@ -846,13 +815,13 @@
     </row>
     <row r="11" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>7</v>
@@ -860,13 +829,13 @@
     </row>
     <row r="12" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>7</v>
@@ -874,13 +843,13 @@
     </row>
     <row r="13" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>7</v>
@@ -888,13 +857,13 @@
     </row>
     <row r="14" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>7</v>
@@ -902,13 +871,13 @@
     </row>
     <row r="15" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>7</v>
@@ -916,10 +885,10 @@
     </row>
     <row r="16" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>24</v>
@@ -930,10 +899,10 @@
     </row>
     <row r="17" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>25</v>
@@ -944,10 +913,10 @@
     </row>
     <row r="18" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>26</v>
@@ -958,27 +927,27 @@
     </row>
     <row r="19" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>7</v>
@@ -986,13 +955,13 @@
     </row>
     <row r="21" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>7</v>
@@ -1000,13 +969,13 @@
     </row>
     <row r="22" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -1014,13 +983,13 @@
     </row>
     <row r="23" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>7</v>
@@ -1028,10 +997,10 @@
     </row>
     <row r="24" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>33</v>
@@ -1042,10 +1011,10 @@
     </row>
     <row r="25" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>34</v>
@@ -1056,10 +1025,10 @@
     </row>
     <row r="26" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>35</v>
@@ -1070,10 +1039,10 @@
     </row>
     <row r="27" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>36</v>
@@ -1084,13 +1053,13 @@
     </row>
     <row r="28" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>7</v>
@@ -1098,13 +1067,13 @@
     </row>
     <row r="29" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>7</v>
@@ -1112,13 +1081,13 @@
     </row>
     <row r="30" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>7</v>
@@ -1126,13 +1095,13 @@
     </row>
     <row r="31" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>7</v>
@@ -1140,13 +1109,13 @@
     </row>
     <row r="32" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>7</v>
@@ -1154,13 +1123,13 @@
     </row>
     <row r="33" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>7</v>
@@ -1168,13 +1137,13 @@
     </row>
     <row r="34" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>7</v>
@@ -1182,13 +1151,13 @@
     </row>
     <row r="35" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>7</v>
@@ -1196,13 +1165,13 @@
     </row>
     <row r="36" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>7</v>
@@ -1210,13 +1179,13 @@
     </row>
     <row r="37" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>7</v>
@@ -1224,13 +1193,13 @@
     </row>
     <row r="38" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>7</v>
@@ -1238,97 +1207,97 @@
     </row>
     <row r="39" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>7</v>
@@ -1336,13 +1305,13 @@
     </row>
     <row r="46" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>7</v>
@@ -1350,13 +1319,13 @@
     </row>
     <row r="47" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>7</v>
@@ -1364,214 +1333,76 @@
     </row>
     <row r="48" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="54" spans="1:4" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
